--- a/Planilhas/Pedidos_logs_2.xlsx
+++ b/Planilhas/Pedidos_logs_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4500030627</t>
+          <t>4500031339</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -492,7 +492,11 @@
           <t>SUCESSO</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031339 modificado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -500,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4500030628</t>
+          <t>4500031340</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,7 +524,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -530,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030628 modificado</t>
+          <t>Pedido Frete 4500031340 modificado</t>
         </is>
       </c>
     </row>
@@ -540,7 +544,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4500030629</t>
+          <t>4500031341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -570,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030629 modificado</t>
+          <t>Pedido Frete 4500031341 modificado</t>
         </is>
       </c>
     </row>
@@ -580,7 +584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4500030630</t>
+          <t>4500031342</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -600,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -610,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030630 modificado</t>
+          <t>Pedido Frete 4500031342 modificado</t>
         </is>
       </c>
     </row>
@@ -620,7 +624,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4500030631</t>
+          <t>4500031343</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,7 +644,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -650,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030631 modificado</t>
+          <t>Pedido Frete 4500031343 modificado</t>
         </is>
       </c>
     </row>
@@ -660,7 +664,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4500030632</t>
+          <t>4500031344</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -680,7 +684,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030632 modificado</t>
+          <t>Pedido Frete 4500031344 modificado</t>
         </is>
       </c>
     </row>
@@ -700,7 +704,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4500030633</t>
+          <t>4500031345</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -720,7 +724,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030633 modificado</t>
+          <t>Pedido Frete 4500031345 modificado</t>
         </is>
       </c>
     </row>
@@ -740,7 +744,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4500030634</t>
+          <t>4500031346</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -770,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030634 modificado</t>
+          <t>Pedido Frete 4500031346 modificado</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4500030635</t>
+          <t>4500031347</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -810,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030635 modificado</t>
+          <t>Pedido Frete 4500031347 modificado</t>
         </is>
       </c>
     </row>
@@ -820,7 +824,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4500030638</t>
+          <t>4500031348</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -840,7 +844,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030638 modificado</t>
+          <t>Pedido Frete 4500031348 modificado</t>
         </is>
       </c>
     </row>
@@ -860,7 +864,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4500030639</t>
+          <t>4500031349</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -880,7 +884,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -890,7 +894,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030639 modificado</t>
+          <t>Pedido Frete 4500031349 modificado</t>
         </is>
       </c>
     </row>
@@ -900,7 +904,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4500030640</t>
+          <t>4500031350</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -920,7 +924,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -930,7 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030640 modificado</t>
+          <t>Pedido Frete 4500031350 modificado</t>
         </is>
       </c>
     </row>
@@ -940,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4500030641</t>
+          <t>4500031351</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -960,7 +964,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -970,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030641 modificado</t>
+          <t>Pedido Frete 4500031351 modificado</t>
         </is>
       </c>
     </row>
@@ -980,7 +984,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4500030642</t>
+          <t>4500031352</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030642 modificado</t>
+          <t>Pedido Frete 4500031352 modificado</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1024,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4500030643</t>
+          <t>4500031353</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1040,7 +1044,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1050,7 +1054,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030643 modificado</t>
+          <t>Pedido Frete 4500031353 modificado</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1064,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4500030646</t>
+          <t>4500031360</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1080,7 +1084,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030646 modificado</t>
+          <t>Pedido Frete 4500031360 modificado</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4500030647</t>
+          <t>4500031361</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1120,7 +1124,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1130,7 +1134,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030647 modificado</t>
+          <t>Pedido Frete 4500031361 modificado</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1144,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4500030648</t>
+          <t>4500031362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1170,7 +1174,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030648 modificado</t>
+          <t>Pedido Frete 4500031362 modificado</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1184,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4500030649</t>
+          <t>4500031363</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1210,7 +1214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030649 modificado</t>
+          <t>Pedido Frete 4500031363 modificado</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1224,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4500030650</t>
+          <t>4500031364</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030650 modificado</t>
+          <t>Pedido Frete 4500031364 modificado</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4500030651</t>
+          <t>4500031365</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1280,7 +1284,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030651 modificado</t>
+          <t>Pedido Frete 4500031365 modificado</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4500030652</t>
+          <t>4500031366</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1330,7 +1334,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030652 modificado</t>
+          <t>Pedido Frete 4500031366 modificado</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1344,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4500030653</t>
+          <t>4500031367</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1360,7 +1364,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030653 modificado</t>
+          <t>Pedido Frete 4500031367 modificado</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1384,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4500030656</t>
+          <t>4500031370</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1400,7 +1404,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030656 modificado</t>
+          <t>Pedido Frete 4500031370 modificado</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1424,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4500030657</t>
+          <t>4500031371</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1440,7 +1444,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030657 modificado</t>
+          <t>Pedido Frete 4500031371 modificado</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1464,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4500030671</t>
+          <t>4500031372</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1480,7 +1484,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030671 modificado</t>
+          <t>Pedido Frete 4500031372 modificado</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4500030672</t>
+          <t>4500031373</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1520,7 +1524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030672 modificado</t>
+          <t>Pedido Frete 4500031373 modificado</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4500030673</t>
+          <t>4500031374</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1560,7 +1564,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1570,7 +1574,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030673 modificado</t>
+          <t>Pedido Frete 4500031374 modificado</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1584,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4500030674</t>
+          <t>4500031375</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1600,7 +1604,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1610,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030674 modificado</t>
+          <t>Pedido Frete 4500031375 modificado</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1624,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4500030675</t>
+          <t>4500031376</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1650,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030675 modificado</t>
+          <t>Pedido Frete 4500031376 modificado</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4500030676</t>
+          <t>4500031391</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1680,7 +1684,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1690,7 +1694,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030676 modificado</t>
+          <t>Pedido Frete 4500031391 modificado</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1704,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4500030677</t>
+          <t>4500031392</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1730,7 +1734,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030677 modificado</t>
+          <t>Pedido Frete 4500031392 modificado</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4500030678</t>
+          <t>4500031393</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1770,7 +1774,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030678 modificado</t>
+          <t>Pedido Frete 4500031393 modificado</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1784,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4500030679</t>
+          <t>4500031394</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1800,7 +1804,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1810,7 +1814,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030679 modificado</t>
+          <t>Pedido Frete 4500031394 modificado</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1824,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4500030680</t>
+          <t>4500031395</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1840,7 +1844,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1850,7 +1854,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030680 modificado</t>
+          <t>Pedido Frete 4500031395 modificado</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1864,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4500030681</t>
+          <t>4500031396</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1890,7 +1894,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030681 modificado</t>
+          <t>Pedido Frete 4500031396 modificado</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1904,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4500030682</t>
+          <t>4500031397</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1920,7 +1924,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1930,7 +1934,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030682 modificado</t>
+          <t>Pedido Frete 4500031397 modificado</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1944,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4500030683</t>
+          <t>4500031398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030683 modificado</t>
+          <t>Pedido Frete 4500031398 modificado</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1984,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4500030684</t>
+          <t>4500031399</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2000,7 +2004,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030684 modificado</t>
+          <t>Pedido Frete 4500031399 modificado</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2024,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4500030685</t>
+          <t>4500031400</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2050,7 +2054,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030685 modificado</t>
+          <t>Pedido Frete 4500031400 modificado</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2064,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4500030686</t>
+          <t>4500031401</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2080,7 +2084,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2090,7 +2094,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030686 modificado</t>
+          <t>Pedido Frete 4500031401 modificado</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2104,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4500030687</t>
+          <t>4500031402</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2120,7 +2124,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2130,7 +2134,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030687 modificado</t>
+          <t>Pedido Frete 4500031402 modificado</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2144,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4500030688</t>
+          <t>4500031403</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2170,7 +2174,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030688 modificado</t>
+          <t>Pedido Frete 4500031403 modificado</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4500030689</t>
+          <t>4500031404</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030689 modificado</t>
+          <t>Pedido Frete 4500031404 modificado</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4500030690</t>
+          <t>4500031405</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2250,7 +2254,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030690 modificado</t>
+          <t>Pedido Frete 4500031405 modificado</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4500030692</t>
+          <t>4500031407</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030692 modificado</t>
+          <t>Pedido Frete 4500031407 modificado</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4500030693</t>
+          <t>4500031408</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030693 modificado</t>
+          <t>Pedido Frete 4500031408 modificado</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2344,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4500030694</t>
+          <t>4500031410</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2360,7 +2364,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030694 modificado</t>
+          <t>Pedido Frete 4500031410 modificado</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2384,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4500030695</t>
+          <t>4500031412</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2400,7 +2404,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2410,7 +2414,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030695 modificado</t>
+          <t>Pedido Frete 4500031412 modificado</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2424,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4500030715</t>
+          <t>4500031413</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2440,7 +2444,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030715 modificado</t>
+          <t>Pedido Frete 4500031413 modificado</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2464,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4500030716</t>
+          <t>4500031414</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2490,7 +2494,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030716 modificado</t>
+          <t>Pedido Frete 4500031414 modificado</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2504,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4500030717</t>
+          <t>4500031415</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2520,7 +2524,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2530,7 +2534,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030717 modificado</t>
+          <t>Pedido Frete 4500031415 modificado</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2544,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4500030718</t>
+          <t>4500031416</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2560,7 +2564,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2570,7 +2574,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030718 modificado</t>
+          <t>Pedido Frete 4500031416 modificado</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2584,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4500030720</t>
+          <t>4500031417</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2610,7 +2614,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030720 modificado</t>
+          <t>Pedido Frete 4500031417 modificado</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4500030721</t>
+          <t>4500031418</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2640,7 +2644,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2650,7 +2654,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030721 modificado</t>
+          <t>Pedido Frete 4500031418 modificado</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4500030722</t>
+          <t>4500031419</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2680,7 +2684,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2690,7 +2694,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030722 modificado</t>
+          <t>Pedido Frete 4500031419 modificado</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4500030723</t>
+          <t>4500031420</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2720,7 +2724,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2730,7 +2734,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030723 modificado</t>
+          <t>Pedido Frete 4500031420 modificado</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2744,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4500030724</t>
+          <t>4500031421</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2770,7 +2774,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030724 modificado</t>
+          <t>Pedido Frete 4500031421 modificado</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2784,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4500030725</t>
+          <t>4500031440</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2800,7 +2804,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2810,7 +2814,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030725 modificado</t>
+          <t>Pedido Frete 4500031440 modificado</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2824,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4500030726</t>
+          <t>4500031441</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2840,7 +2844,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2850,7 +2854,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500030726 modificado</t>
+          <t>Pedido Frete 4500031441 modificado</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2864,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4500030727</t>
+          <t>4500031442</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2880,7 +2884,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2888,7 +2892,651 @@
           <t>SUCESSO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031442 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>4500031443</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031443 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4500031444</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031444 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>65</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4500031445</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031445 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4500031446</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031446 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4500031447</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031447 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4500031448</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031448 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>4500031449</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031449 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4500031450</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031450 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4500031451</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031451 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4500031452</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031452 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>4500031453</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031453 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4500031454</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031454 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4500031455</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031455 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4500031456</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031456 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4500031457</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031457 modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4500031458</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RAZAO</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3201010111</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Pedido Frete 4500031458 modificado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
